--- a/p6_deployment/data/france/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/france/data_preparation/format_data/df_match_odds_form.xlsx
@@ -448,145 +448,145 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>88K4TzrO</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="C2" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2ek4VdDB</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.33</v>
+        <v>3.25</v>
       </c>
       <c r="C3" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>naJ8SfcU</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="C4" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="D4" t="n">
-        <v>6.25</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Yk0Wxb5</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.62</v>
+        <v>6.25</v>
       </c>
       <c r="C5" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>xObInbrn</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="C6" t="n">
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
       <c r="D6" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OKfEmvTu</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.75</v>
+        <v>2.05</v>
       </c>
       <c r="C7" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>tnl8UGSH</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.48</v>
+        <v>3.5</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="D8" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>fVodXIra</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="C9" t="n">
         <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>C6diYbTh</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="C10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D10" t="n">
         <v>3.6</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2.3</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/france/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/france/data_preparation/format_data/df_match_odds_form.xlsx
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="C4" t="n">
         <v>3.4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="6">
